--- a/src/tests/测试用例-功能测试.xlsx
+++ b/src/tests/测试用例-功能测试.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="14190" windowHeight="10440"/>
+    <workbookView windowWidth="20750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="269">
   <si>
     <t>DDL测试用例表</t>
   </si>
@@ -68,7 +68,7 @@
     <t>p0</t>
   </si>
   <si>
-    <t>1.打开表单填写界面
+    <t>1.打开任务创建
 2.网络连接正常</t>
   </si>
   <si>
@@ -149,102 +149,105 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>DDL_clip_001</t>
-  </si>
-  <si>
-    <t>剪贴板添加任务成功（剪贴板有内容）</t>
-  </si>
-  <si>
-    <t>1.点击“剪贴板”进入界面
-2.剪贴板已有复制内容
-3.网络连接正常</t>
-  </si>
-  <si>
-    <t>1.点击读取剪贴板
-2.点击保存</t>
-  </si>
-  <si>
-    <t>剪贴板内容：明天早上十点上课</t>
-  </si>
-  <si>
-    <t>剪贴便识别成功，显示：已读取剪贴板内容
-任务创建成功</t>
-  </si>
-  <si>
-    <t>DDL_clip_002</t>
-  </si>
-  <si>
-    <t>剪贴板添加任务失败（剪贴板无内容）</t>
-  </si>
-  <si>
-    <t>1.点击剪切板进入识别界面
-2.剪贴板无复制内容
-3.网络连接正常</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.点击读取剪贴板
-2.点击保存 </t>
+    <t>DDL_color_001</t>
+  </si>
+  <si>
+    <t>任务优先级显示红色（重要且紧急）</t>
+  </si>
+  <si>
+    <t>p2</t>
+  </si>
+  <si>
+    <t>1.输入任务标题
+2.选择优先级
+3.点击保存</t>
+  </si>
+  <si>
+    <t>任务标题：1
+优先级：重要且紧急</t>
+  </si>
+  <si>
+    <t>任务创建成功，优先级显示红色</t>
+  </si>
+  <si>
+    <t>DDL_color_002</t>
+  </si>
+  <si>
+    <t>任务优先级显示橙色（紧急但不重要）</t>
+  </si>
+  <si>
+    <t>任务标题：2
+优先级：紧急但不重要</t>
+  </si>
+  <si>
+    <t>任务创建成功，优先级显示橙色</t>
+  </si>
+  <si>
+    <t>DDL_color_003</t>
+  </si>
+  <si>
+    <t>任务优先级显示绿色（重要但不紧急）</t>
+  </si>
+  <si>
+    <t>任务标题：3
+优先级：重要但不紧急</t>
+  </si>
+  <si>
+    <t>任务创建成功，优先级显示绿色</t>
+  </si>
+  <si>
+    <t>DDL_color_004</t>
+  </si>
+  <si>
+    <t>任务优先级显示灰色（不重要不紧急）</t>
+  </si>
+  <si>
+    <t>任务标题：4
+优先级：不重要不紧急</t>
+  </si>
+  <si>
+    <t>任务创建成功，优先级显示灰色</t>
+  </si>
+  <si>
+    <t>DDL_AI_001</t>
+  </si>
+  <si>
+    <t>AI解析添加任务成功（剪贴板有内容）</t>
+  </si>
+  <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>1.使用ai解析创建任务
+2.点击智能解析
+3.点击填入表单
+4.点击保存</t>
+  </si>
+  <si>
+    <t>ai解析内容：明天早上十点上课</t>
+  </si>
+  <si>
+    <t>解析成功，点击填入表单，任务创建成功</t>
+  </si>
+  <si>
+    <t>DDL_AI_002</t>
+  </si>
+  <si>
+    <t>AI拆解任务（任务可拆解）</t>
+  </si>
+  <si>
+    <t>1.已存在任务
+2.网络连接正常</t>
+  </si>
+  <si>
+    <t>1.点击任务右边的AI拆解任务
+2.点击“采纳为子任务备注”</t>
   </si>
   <si>
     <t>/</t>
   </si>
   <si>
-    <t>剪贴板无法识别出内容
-无法创建任务，提示：请输入任务标题</t>
-  </si>
-  <si>
-    <t>DDL_voice_001</t>
-  </si>
-  <si>
-    <t>语音录入添加任务成功（语音清晰明确）</t>
-  </si>
-  <si>
-    <t>1.打开“语音录入”进入界面
-2.麦克风权限已授权
-3.网络连接正常</t>
-  </si>
-  <si>
-    <t>1.点击“开始语音输入”
-2.说出“明天早上十点上课”
-3.点击保存</t>
-  </si>
-  <si>
-    <t>语音内容：明天早上十点上课</t>
-  </si>
-  <si>
-    <t>语音识别成功，显示：已读取语音内容
-任务创建成功</t>
-  </si>
-  <si>
-    <t>DDL_voice_002</t>
-  </si>
-  <si>
-    <t>语音录入添加任务失败（语音模糊）</t>
-  </si>
-  <si>
-    <t>1.点击“开始语音输入”
-2.语音小声或嘈杂
-3.点击保存</t>
-  </si>
-  <si>
-    <t xml:space="preserve">显示：语音识别失败 </t>
-  </si>
-  <si>
-    <t>DDL_voice_003</t>
-  </si>
-  <si>
-    <t>语音录入添加任务失败（未开启麦克风权限）</t>
-  </si>
-  <si>
-    <t>1.打开“语音录入”进入界面
-2.麦克风未授权
-3.网络连接正常</t>
-  </si>
-  <si>
-    <t>1.点击“开始语音输入”</t>
-  </si>
-  <si>
-    <t>显示未开启麦克风权限</t>
+    <t>ai拆解成功，已将拆解内容添加到任务说明</t>
   </si>
   <si>
     <t>DDL_edit_001</t>
@@ -332,6 +335,23 @@
 3.点击保存</t>
   </si>
   <si>
+    <t>DDL_delete_001</t>
+  </si>
+  <si>
+    <t>删除任务成功</t>
+  </si>
+  <si>
+    <t>删除</t>
+  </si>
+  <si>
+    <t>1.点击任务进入详情页
+2.点击右上角“删除”
+3.点击确认删除</t>
+  </si>
+  <si>
+    <t>任务删除成功</t>
+  </si>
+  <si>
     <t>DDL_filter_001</t>
   </si>
   <si>
@@ -501,6 +521,10 @@
     <t>目标栏/象限</t>
   </si>
   <si>
+    <t>1.打开表单填写界面
+2.网络连接正常</t>
+  </si>
+  <si>
     <t>1.输入任务标题
 2.点击保存</t>
   </si>
@@ -839,7 +863,7 @@
   </si>
   <si>
     <t>1.网络连接正常
-2.已设置邮箱地址</t>
+2.已保存邮箱地址</t>
   </si>
   <si>
     <t>1.点击“我的”菜单栏
@@ -847,23 +871,6 @@
   </si>
   <si>
     <t>已打开邮箱提醒</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DDL_remind_003</t>
-  </si>
-  <si>
-    <t>开启应用内弹窗（点开开关）</t>
-  </si>
-  <si>
-    <t>1.网络连接正常
-2.本机已设置允许弹窗</t>
-  </si>
-  <si>
-    <t>1.点击“我的”菜单栏
-2.点击开启应用内弹窗开关</t>
-  </si>
-  <si>
-    <t>已打开应用内弹窗</t>
   </si>
   <si>
     <t xml:space="preserve"> DDL_remind_004</t>
@@ -933,7 +940,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -969,12 +976,6 @@
       <sz val="11.5"/>
       <color rgb="FF0F1115"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11.25"/>
-      <color rgb="FF0F1115"/>
-      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1497,137 +1498,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1661,13 +1662,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2204,7 +2202,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:K57"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="23.6363636363636" style="2" customWidth="1"/>
@@ -2364,20 +2362,20 @@
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="42" spans="1:11">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="12" t="s">
         <v>34</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>36</v>
@@ -2385,689 +2383,687 @@
       <c r="G7" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="10" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="42" spans="1:11">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="12" t="s">
         <v>40</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="E8" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="H8" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="G8" s="9" t="s">
+    </row>
+    <row r="9" s="1" customFormat="1" ht="42" spans="1:11">
+      <c r="A9" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="B9" s="12" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="56" spans="1:11">
-      <c r="A9" s="8" t="s">
+      <c r="C9" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="H9" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="9" t="s">
+    </row>
+    <row r="10" s="1" customFormat="1" ht="42" spans="1:11">
+      <c r="A10" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="B10" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="C10" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H10" s="10" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" ht="56" spans="1:11">
-      <c r="A10" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="56" spans="1:11">
       <c r="A11" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="H11" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="9" t="s">
+    </row>
+    <row r="12" s="1" customFormat="1" ht="28" spans="1:11">
+      <c r="A12" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="B12" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="G11" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="H11" s="9" t="s">
+      <c r="C12" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="9" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="12" customFormat="1" ht="42" spans="1:11">
-      <c r="A12" s="2" t="s">
+      <c r="F12" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="B12" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="C12" s="8" t="s">
+      <c r="G12" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H12" s="9" t="s">
         <v>62</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="G12" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="13" customFormat="1" ht="42" spans="1:11">
       <c r="A13" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F13" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="G13" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F13" s="9" t="s">
+      <c r="H13" s="10" t="s">
         <v>69</v>
-      </c>
-      <c r="G13" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="14" customFormat="1" ht="42" spans="1:11">
       <c r="A14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="C14" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F14" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F14" s="9" t="s">
+      <c r="G14" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="H14" s="10" t="s">
         <v>73</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="15" customFormat="1" ht="42" spans="1:11">
       <c r="A15" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B15" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="C15" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F15" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F15" s="9" t="s">
+      <c r="G15" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="G15" s="14"/>
       <c r="H15" s="10" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" customFormat="1" ht="42" spans="1:11">
       <c r="A16" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="11" t="s">
         <v>79</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>12</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="G16" s="14"/>
+      <c r="G16" s="13"/>
       <c r="H16" s="10" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" customFormat="1" ht="42" spans="1:8">
       <c r="A17" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="11" t="s">
         <v>82</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>12</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="G17" s="14"/>
+      <c r="G17" s="13"/>
       <c r="H17" s="10" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="18" ht="28" spans="1:8">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" customFormat="1" ht="42" spans="1:8">
       <c r="A18" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="11" t="s">
         <v>85</v>
       </c>
       <c r="C18" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F18" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="D18" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F18" s="9" t="s">
+      <c r="G18" s="13"/>
+      <c r="H18" s="10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" ht="42" spans="1:8">
+      <c r="A19" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G18" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H18" s="10" t="s">
+      <c r="B19" s="11" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="19" ht="28" spans="1:8">
-      <c r="A19" s="2" t="s">
+      <c r="C19" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="D19" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F19" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" s="9" t="s">
+      <c r="G19" s="13"/>
+      <c r="H19" s="10" t="s">
         <v>91</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="20" ht="28" spans="1:8">
       <c r="A20" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="D20" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F20" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C20" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" s="9" t="s">
+      <c r="G20" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H20" s="10" t="s">
         <v>96</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H20" s="10" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="21" ht="28" spans="1:8">
       <c r="A21" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="F21" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E21" s="9" t="s">
+      <c r="G21" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H21" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="F21" s="9" t="s">
+    </row>
+    <row r="22" ht="28" spans="1:8">
+      <c r="A22" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="G21" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H21" s="10" t="s">
+      <c r="B22" s="8" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="2" t="s">
+      <c r="C22" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="F22" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22" s="10" t="s">
+      <c r="G22" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H22" s="10" t="s">
         <v>106</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="G22" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H22" s="10" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="23" ht="28" spans="1:8">
       <c r="A23" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="F23" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="C23" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E23" s="9" t="s">
+      <c r="G23" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H23" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="F23" s="9" t="s">
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="G23" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H23" s="10" t="s">
+      <c r="B24" s="8" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="24" ht="42" spans="1:8">
-      <c r="A24" s="2" t="s">
+      <c r="C24" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="F24" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="C24" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E24" s="9" t="s">
+      <c r="G24" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H24" s="10" t="s">
         <v>116</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="G24" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="25" ht="28" spans="1:8">
       <c r="A25" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="F25" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="C25" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E25" s="9" t="s">
+      <c r="G25" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="F25" s="9" t="s">
+    </row>
+    <row r="26" ht="42" spans="1:8">
+      <c r="A26" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="G25" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H25" s="9" t="s">
+      <c r="B26" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="26" ht="28" spans="1:8">
-      <c r="A26" s="2" t="s">
+      <c r="C26" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="F26" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="G26" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H26" s="9" t="s">
         <v>126</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="F26" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="G26" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H26" s="10" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="27" ht="28" spans="1:8">
       <c r="A27" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="F27" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="G27" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H27" s="9" t="s">
         <v>131</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="G27" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="28" ht="28" spans="1:8">
       <c r="A28" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C28" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="D28" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="F28" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="D28" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F28" s="9" t="s">
+      <c r="G28" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H28" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="G28" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H28" s="10" t="s">
+    </row>
+    <row r="29" ht="28" spans="1:8">
+      <c r="A29" s="2" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="29" ht="42" spans="1:8">
-      <c r="A29" s="2" t="s">
+      <c r="B29" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="C29" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="F29" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="D29" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F29" s="9" t="s">
+      <c r="G29" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="G29" s="10" t="s">
+    </row>
+    <row r="30" ht="28" spans="1:8">
+      <c r="A30" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="H29" s="10" t="s">
+      <c r="B30" s="8" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="30" ht="42" spans="1:8">
-      <c r="A30" s="2" t="s">
+      <c r="C30" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="D30" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="C30" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>63</v>
-      </c>
       <c r="F30" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="G30" s="14" t="s">
-        <v>43</v>
+        <v>146</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>61</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="31" ht="42" spans="1:8">
       <c r="A31" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>12</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>43</v>
+        <v>151</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="32" ht="28" spans="1:8">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="32" ht="42" spans="1:8">
       <c r="A32" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>12</v>
       </c>
       <c r="E32" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="H32" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="F32" s="10" t="s">
+    </row>
+    <row r="33" ht="42" spans="1:8">
+      <c r="A33" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="G32" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H32" s="10" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="33" ht="28" spans="1:8">
-      <c r="A33" s="2" t="s">
+      <c r="B33" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="C33" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E33" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="F33" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="D33" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="F33" s="10" t="s">
+      <c r="G33" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H33" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="34" ht="28" spans="1:8">
       <c r="A34" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B34" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="C34" s="8" t="s">
         <v>162</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>158</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>12</v>
@@ -3075,37 +3071,37 @@
       <c r="E34" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="F34" s="9" t="s">
+      <c r="F34" s="10" t="s">
         <v>164</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>165</v>
+        <v>96</v>
       </c>
     </row>
     <row r="35" ht="28" spans="1:8">
       <c r="A35" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B35" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="C35" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="C35" s="8" t="s">
-        <v>158</v>
-      </c>
       <c r="D35" s="8" t="s">
         <v>12</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="F35" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="F35" s="10" t="s">
         <v>168</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="H35" s="10" t="s">
         <v>169</v>
@@ -3119,19 +3115,19 @@
         <v>171</v>
       </c>
       <c r="C36" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36" s="9" t="s">
         <v>172</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>154</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>173</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="H36" s="10" t="s">
         <v>174</v>
@@ -3145,33 +3141,33 @@
         <v>176</v>
       </c>
       <c r="C37" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="F37" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="D37" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="F37" s="9" t="s">
+      <c r="G37" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="G37" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H37" s="10" t="s">
+    </row>
+    <row r="38" ht="28" spans="1:8">
+      <c r="A38" s="2" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="38" ht="42" spans="1:8">
-      <c r="A38" s="2" t="s">
+      <c r="B38" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="B38" s="8" t="s">
-        <v>162</v>
-      </c>
       <c r="C38" s="8" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D38" s="8" t="s">
         <v>12</v>
@@ -3180,65 +3176,65 @@
         <v>163</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="39" ht="42" spans="1:8">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="39" ht="28" spans="1:8">
       <c r="A39" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>12</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="40" ht="28" spans="1:8">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="40" ht="42" spans="1:8">
       <c r="A40" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="C40" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="B40" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>188</v>
-      </c>
       <c r="D40" s="8" t="s">
         <v>12</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
     </row>
     <row r="41" ht="42" spans="1:8">
@@ -3249,7 +3245,7 @@
         <v>192</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>12</v>
@@ -3261,13 +3257,13 @@
         <v>193</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="H41" s="10" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="42" ht="42" spans="1:8">
+    <row r="42" ht="28" spans="1:8">
       <c r="A42" s="2" t="s">
         <v>195</v>
       </c>
@@ -3275,305 +3271,305 @@
         <v>196</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>12</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F42" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="G42" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H42" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="43" ht="42" spans="1:8">
+      <c r="A43" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="C43" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="G42" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H42" s="10" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="43" ht="28" spans="1:8">
-      <c r="A43" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>201</v>
-      </c>
       <c r="D43" s="8" t="s">
         <v>12</v>
       </c>
       <c r="E43" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F43" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="F43" s="10" t="s">
+      <c r="G43" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H43" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="G43" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H43" s="10" t="s">
+    </row>
+    <row r="44" ht="42" spans="1:8">
+      <c r="A44" s="2" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="44" ht="28" spans="1:8">
-      <c r="A44" s="2" t="s">
+      <c r="B44" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="C44" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="F44" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="C44" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E44" s="9" t="s">
+      <c r="G44" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H44" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="F44" s="9" t="s">
+    </row>
+    <row r="45" ht="28" spans="1:8">
+      <c r="A45" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="G44" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H44" s="10" t="s">
+      <c r="B45" s="8" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" s="2" t="s">
+      <c r="C45" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="D45" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E45" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="F45" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="D45" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E45" s="15" t="s">
+      <c r="G45" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>213</v>
-      </c>
-      <c r="F45" s="15" t="s">
-        <v>214</v>
-      </c>
-      <c r="G45" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="H45" s="15" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="46" ht="28" spans="1:8">
       <c r="A46" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E46" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="F46" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="C46" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E46" s="15" t="s">
-        <v>213</v>
-      </c>
-      <c r="F46" s="16" t="s">
+      <c r="G46" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H46" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="G46" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="H46" t="s">
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="2" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="47" ht="28" spans="1:8">
-      <c r="A47" s="2" t="s">
+      <c r="B47" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="C47" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="C47" s="8" t="s">
-        <v>212</v>
-      </c>
       <c r="D47" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E47" s="15" t="s">
-        <v>213</v>
-      </c>
-      <c r="F47" s="16" t="s">
+      <c r="E47" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="G47" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="H47" t="s">
+      <c r="F47" s="14" t="s">
         <v>223</v>
+      </c>
+      <c r="G47" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="H47" s="14" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="48" ht="28" spans="1:8">
       <c r="A48" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="D48" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E48" s="15" t="s">
-        <v>213</v>
-      </c>
-      <c r="F48" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="G48" s="15" t="s">
-        <v>43</v>
+      <c r="E48" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="F48" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="G48" s="14" t="s">
+        <v>61</v>
       </c>
       <c r="H48" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="49" ht="28" spans="1:8">
       <c r="A49" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="D49" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E49" s="15" t="s">
-        <v>213</v>
-      </c>
-      <c r="F49" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="G49" s="15" t="s">
-        <v>43</v>
+      <c r="E49" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="F49" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="G49" s="14" t="s">
+        <v>61</v>
       </c>
       <c r="H49" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="50" ht="28" spans="1:8">
       <c r="A50" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="D50" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E50" s="16" t="s">
+      <c r="E50" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="F50" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="F50" s="16" t="s">
+      <c r="G50" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="H50" t="s">
         <v>236</v>
-      </c>
-      <c r="G50" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="H50" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="51" ht="28" spans="1:8">
       <c r="A51" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="C51" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E51" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="F51" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="C51" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="D51" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E51" s="16" t="s">
+      <c r="G51" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="H51" t="s">
         <v>240</v>
-      </c>
-      <c r="F51" s="16" t="s">
-        <v>241</v>
-      </c>
-      <c r="G51" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="H51" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="52" ht="28" spans="1:8">
       <c r="A52" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C52" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="D52" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E52" s="15" t="s">
         <v>244</v>
       </c>
-      <c r="C52" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="D52" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E52" s="16" t="s">
+      <c r="F52" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="F52" s="16" t="s">
+      <c r="G52" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="H52" t="s">
         <v>246</v>
-      </c>
-      <c r="G52" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="H52" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="53" ht="28" spans="1:8">
       <c r="A53" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="C53" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E53" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="C53" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="D53" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E53" s="15" t="s">
-        <v>213</v>
-      </c>
-      <c r="F53" s="16" t="s">
+      <c r="F53" s="15" t="s">
         <v>250</v>
       </c>
-      <c r="G53" s="15" t="s">
-        <v>43</v>
+      <c r="G53" s="14" t="s">
+        <v>61</v>
       </c>
       <c r="H53" t="s">
         <v>251</v>
@@ -3587,25 +3583,25 @@
         <v>253</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="D54" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E54" s="15" t="s">
-        <v>213</v>
-      </c>
-      <c r="F54" s="16" t="s">
+      <c r="E54" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="F54" s="15" t="s">
         <v>254</v>
       </c>
-      <c r="G54" s="15" t="s">
-        <v>43</v>
+      <c r="G54" s="14" t="s">
+        <v>61</v>
       </c>
       <c r="H54" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="55" ht="42" spans="1:8">
+    <row r="55" ht="28" spans="1:8">
       <c r="A55" s="2" t="s">
         <v>256</v>
       </c>
@@ -3613,48 +3609,74 @@
         <v>257</v>
       </c>
       <c r="C55" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E55" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="F55" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="D55" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E55" s="15" t="s">
-        <v>213</v>
-      </c>
-      <c r="F55" s="16" t="s">
+      <c r="G55" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="H55" t="s">
         <v>259</v>
-      </c>
-      <c r="G55" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="H55" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="56" ht="42" spans="1:8">
       <c r="A56" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="C56" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="C56" s="8" t="s">
-        <v>258</v>
-      </c>
       <c r="D56" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E56" s="15" t="s">
-        <v>213</v>
-      </c>
-      <c r="F56" s="16" t="s">
+      <c r="E56" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="F56" s="15" t="s">
         <v>263</v>
       </c>
-      <c r="G56" s="15" t="s">
-        <v>43</v>
+      <c r="G56" s="14" t="s">
+        <v>61</v>
       </c>
       <c r="H56" t="s">
         <v>264</v>
+      </c>
+    </row>
+    <row r="57" ht="42" spans="1:8">
+      <c r="A57" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E57" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="F57" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="G57" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="H57" t="s">
+        <v>268</v>
       </c>
     </row>
   </sheetData>

--- a/src/tests/测试用例-功能测试.xlsx
+++ b/src/tests/测试用例-功能测试.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="416">
   <si>
     <t>DDL测试用例表</t>
   </si>
@@ -56,6 +56,136 @@
     <t>预期结果</t>
   </si>
   <si>
+    <t>DDL_user_001</t>
+  </si>
+  <si>
+    <t>创建用户成功（合法id）</t>
+  </si>
+  <si>
+    <t>新建用户</t>
+  </si>
+  <si>
+    <t>p0</t>
+  </si>
+  <si>
+    <t>1.未登录或已登录任意用户
+2.网络连接正常</t>
+  </si>
+  <si>
+    <t>1. 点击新建用户
+2. 输入用户ID
+3. 输入昵称
+4. 点击创建并切换</t>
+  </si>
+  <si>
+    <t>用户ID: 001user_001--
+昵称：学生</t>
+  </si>
+  <si>
+    <t>用户已创建并切换</t>
+  </si>
+  <si>
+    <t>DDL_user_002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">创建用户成功（id边界值：最小长度2位） </t>
+  </si>
+  <si>
+    <t>用户ID: 01
+昵称：学生</t>
+  </si>
+  <si>
+    <t>DDL_user_003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">创建用户成功（id边界值：最大长度32位） </t>
+  </si>
+  <si>
+    <t>用户ID: 12345678912345678912345678912345
+昵称：学生</t>
+  </si>
+  <si>
+    <t>DDL_user_004</t>
+  </si>
+  <si>
+    <t>创建用户失败（id为空）</t>
+  </si>
+  <si>
+    <t>p1</t>
+  </si>
+  <si>
+    <t>1. 点击新建用户
+2. 输入昵称
+3. 点击创建并切换</t>
+  </si>
+  <si>
+    <t>昵称：学生</t>
+  </si>
+  <si>
+    <t>无法创建，用户ID不能为空</t>
+  </si>
+  <si>
+    <t>DDL_user_005</t>
+  </si>
+  <si>
+    <t>创建用户失败（id为1位）</t>
+  </si>
+  <si>
+    <t>用户ID: 1
+昵称：学生</t>
+  </si>
+  <si>
+    <t>无法创建，用户ID仅支持2-32位字母、数字、下划线、连字符</t>
+  </si>
+  <si>
+    <t>DDL_user_006</t>
+  </si>
+  <si>
+    <t>创建用户失败（id为33位）</t>
+  </si>
+  <si>
+    <t>用户ID: 123456789123456789123456789123456
+昵称：学生</t>
+  </si>
+  <si>
+    <t>DDL_user_007</t>
+  </si>
+  <si>
+    <t>创建用户失败（id包含中文）</t>
+  </si>
+  <si>
+    <t>用户ID: 李华
+昵称：学生</t>
+  </si>
+  <si>
+    <t>DDL_user_008</t>
+  </si>
+  <si>
+    <t>创建用户失败（id包含非法字符）</t>
+  </si>
+  <si>
+    <t>用户ID: 1@#￥ 2
+昵称：学生</t>
+  </si>
+  <si>
+    <t>DDL_user_009</t>
+  </si>
+  <si>
+    <t>创建用户失败（id已存在）</t>
+  </si>
+  <si>
+    <t>1.未登录或已登录任意用户
+2.网络连接正常
+3.存在已创建的用户</t>
+  </si>
+  <si>
+    <t>用户ID: 和已存在的用户id一样
+昵称：学生</t>
+  </si>
+  <si>
+    <t>用户已存在，直接切换到该用户</t>
+  </si>
+  <si>
     <t>DDL_add_001</t>
   </si>
   <si>
@@ -63,9 +193,6 @@
   </si>
   <si>
     <t>添加任务</t>
-  </si>
-  <si>
-    <t>p0</t>
   </si>
   <si>
     <t>1.打开任务创建
@@ -112,9 +239,6 @@
     <t>添加任务失败（不填写任务标题）</t>
   </si>
   <si>
-    <t>p1</t>
-  </si>
-  <si>
     <t>1.不输入任务标题
 2.点击保存</t>
   </si>
@@ -212,10 +336,15 @@
     <t>DDL_AI_001</t>
   </si>
   <si>
-    <t>AI解析添加任务成功（剪贴板有内容）</t>
+    <t>AI解析添加任务成功（基础解析）</t>
   </si>
   <si>
     <t>AI</t>
+  </si>
+  <si>
+    <t>1.打开任务创建
+2.确认 AI 智能解析服务已正常连接
+3.网络连接正常</t>
   </si>
   <si>
     <t>1.使用ai解析创建任务
@@ -224,13 +353,266 @@
 4.点击保存</t>
   </si>
   <si>
-    <t>ai解析内容：明天早上十点上课</t>
-  </si>
-  <si>
-    <t>解析成功，点击填入表单，任务创建成功</t>
+    <t>ai解析内容：5.19日早上十点上课，重要不紧急，分类学习</t>
+  </si>
+  <si>
+    <t>解析成功：
+标题:上课，优先级：重要不紧急，分类：学习，截止时间：5.19日早上十点。
+点击填入表单，任务创建成功</t>
   </si>
   <si>
     <t>DDL_AI_002</t>
+  </si>
+  <si>
+    <t>AI解析添加任务成功（复杂指令）</t>
+  </si>
+  <si>
+    <t>ai解析内容：完成这周的三个紧急报告：财务分析、市场调研、竞品分析，周五之前</t>
+  </si>
+  <si>
+    <t>解析成功：
+分别创建三个任务
+点击填入表单，任务创建成功</t>
+  </si>
+  <si>
+    <t>DDL_AI_003</t>
+  </si>
+  <si>
+    <t>AI解析添加任务成功（重复性任务）</t>
+  </si>
+  <si>
+    <t>ai解析内容：每天晚上九点跑步</t>
+  </si>
+  <si>
+    <t>解析成功：
+标题:跑步，优先级：重要不紧急，分类：健康，截止时间：晚上九点。
+点击填入表单，任务创建成功</t>
+  </si>
+  <si>
+    <t>DDL_AI_004</t>
+  </si>
+  <si>
+    <t>AI解析添加任务成功（绝对时间）</t>
+  </si>
+  <si>
+    <t>ai解析内容：今天晚上九点之前跑步</t>
+  </si>
+  <si>
+    <t>DDL_AI_005</t>
+  </si>
+  <si>
+    <t>AI解析添加任务成功（相对时间）</t>
+  </si>
+  <si>
+    <t>ai解析内容：2026年5月21日13点午休</t>
+  </si>
+  <si>
+    <t>解析成功：
+标题:午休，优先级：不重要不紧急，分类：生活，截止时间：2026年5月21日13点
+点击填入表单，任务创建成功</t>
+  </si>
+  <si>
+    <t>DDL_AI_006</t>
+  </si>
+  <si>
+    <t>AI解析添加任务成功（模糊时间）</t>
+  </si>
+  <si>
+    <t>ai解析内容：明天14点午休</t>
+  </si>
+  <si>
+    <t>解析成功：
+标题:午休，优先级：不重要不紧急，分类：生活，截止时间：明天14点
+点击填入表单，任务创建成功</t>
+  </si>
+  <si>
+    <t>DDL_AI_007</t>
+  </si>
+  <si>
+    <t>AI解析添加任务成功（截止日期）</t>
+  </si>
+  <si>
+    <t>ai解析内容：明天中午午休</t>
+  </si>
+  <si>
+    <t>解析成功：
+标题:午休，优先级：不重要不紧急，分类：生活，截止时间：明天13点
+点击填入表单，任务创建成功</t>
+  </si>
+  <si>
+    <t>DDL_AI_008</t>
+  </si>
+  <si>
+    <t>AI解析添加任务成功（重要且紧急）</t>
+  </si>
+  <si>
+    <t>ai解析内容：完成作业，必须在今天下午 5 点前</t>
+  </si>
+  <si>
+    <t>解析成功：
+优先级：重要且紧急
+点击填入表单，任务创建成功</t>
+  </si>
+  <si>
+    <t>DDL_AI_009</t>
+  </si>
+  <si>
+    <t>AI解析添加任务成功（重要不紧急）</t>
+  </si>
+  <si>
+    <t>ai解析内容：下个月给朋友过生日</t>
+  </si>
+  <si>
+    <t>解析成功：
+优先级：重要不紧急
+点击填入表单，任务创建成功</t>
+  </si>
+  <si>
+    <t>DDL_AI_010</t>
+  </si>
+  <si>
+    <t>AI解析添加任务成功（紧急不重要）</t>
+  </si>
+  <si>
+    <t>ai解析内容：一小时后帮朋友买奶茶</t>
+  </si>
+  <si>
+    <t>解析成功：
+优先级：紧急不重要
+点击填入表单，任务创建成功</t>
+  </si>
+  <si>
+    <t>DDL_AI_011</t>
+  </si>
+  <si>
+    <t>AI解析添加任务成功（不紧急不重要）</t>
+  </si>
+  <si>
+    <t>ai解析内容：有空的时候看剧</t>
+  </si>
+  <si>
+    <t>解析成功：
+优先级：不重要不紧急
+点击填入表单，任务创建成功</t>
+  </si>
+  <si>
+    <t>DDL_AI_012</t>
+  </si>
+  <si>
+    <t>AI解析添加任务成功（极简指令）</t>
+  </si>
+  <si>
+    <t>ai解析内容：上课</t>
+  </si>
+  <si>
+    <t>解析成功：
+标题:上课，优先级：默认 重要不紧急，分类：学习，时间：无
+点击填入表单，任务创建成功</t>
+  </si>
+  <si>
+    <t>DDL_AI_013</t>
+  </si>
+  <si>
+    <t>AI解析添加任务成功（仅时间指令）</t>
+  </si>
+  <si>
+    <t>ai解析内容：明天</t>
+  </si>
+  <si>
+    <t>解析成功：
+标题:明天，优先级：默认 不重要不紧急，分类：其他，截止时间：明天23:59
+点击填入表单，任务创建成功</t>
+  </si>
+  <si>
+    <t>DDL_AI_014</t>
+  </si>
+  <si>
+    <t>AI解析添加任务成功（分类学习）</t>
+  </si>
+  <si>
+    <t>ai解析内容：今天晚上八点上课</t>
+  </si>
+  <si>
+    <t>解析成功：
+分类：学习
+点击填入表单，任务创建成功</t>
+  </si>
+  <si>
+    <t>DDL_AI_015</t>
+  </si>
+  <si>
+    <t>AI解析添加任务成功（分类生活）</t>
+  </si>
+  <si>
+    <t>ai解析内容：今晚六点吃饭</t>
+  </si>
+  <si>
+    <t>解析成功：
+分类：生活
+点击填入表单，任务创建成功</t>
+  </si>
+  <si>
+    <t>DDL_AI_016</t>
+  </si>
+  <si>
+    <t>AI解析添加任务成功（分类健康）</t>
+  </si>
+  <si>
+    <t>ai解析内容：今晚八点跑步</t>
+  </si>
+  <si>
+    <t>解析成功：
+分类：健康
+点击填入表单，任务创建成功</t>
+  </si>
+  <si>
+    <t>DDL_AI_017</t>
+  </si>
+  <si>
+    <t>AI解析添加任务成功（分类娱乐）</t>
+  </si>
+  <si>
+    <t>ai解析内容：今晚十点看电影</t>
+  </si>
+  <si>
+    <t>解析成功：
+分类：娱乐
+点击填入表单，任务创建成功</t>
+  </si>
+  <si>
+    <t>DDL_AI_018</t>
+  </si>
+  <si>
+    <t>AI解析添加任务成功（分类工作）</t>
+  </si>
+  <si>
+    <t>ai解析内容：明天十点开会</t>
+  </si>
+  <si>
+    <t>解析成功：
+分类：工作
+点击填入表单，任务创建成功</t>
+  </si>
+  <si>
+    <t>DDL_AI_019</t>
+  </si>
+  <si>
+    <t>AI解析添加任务失败（网络断开）</t>
+  </si>
+  <si>
+    <t>1.打开任务创建
+2.确认 AI 智能解析服务已正常连接
+3.网络断开</t>
+  </si>
+  <si>
+    <t>1.使用ai解析创建任务
+2.点击智能解析</t>
+  </si>
+  <si>
+    <t>无法解析，网络断开</t>
+  </si>
+  <si>
+    <t>DDL_AI_021</t>
   </si>
   <si>
     <t>AI拆解任务（任务可拆解）</t>
@@ -405,7 +787,7 @@
     <t>筛选“临期”任务</t>
   </si>
   <si>
-    <t>1.存在临期的任务
+    <t>1.存在24h内的临期的任务
 2.网络连接正常</t>
   </si>
   <si>
@@ -571,13 +953,13 @@
     <t>重要且紧急象限里的“上课”任务已消失</t>
   </si>
   <si>
-    <t>DDL_quadrant_005</t>
-  </si>
-  <si>
-    <t>列表正确显示</t>
-  </si>
-  <si>
-    <t>目标栏/列表</t>
+    <t>DDL_target_001</t>
+  </si>
+  <si>
+    <t>目标列表正确显示</t>
+  </si>
+  <si>
+    <t>目标</t>
   </si>
   <si>
     <t>1. 已存在任务
@@ -585,6 +967,128 @@
   </si>
   <si>
     <t>1.点击“列表”栏</t>
+  </si>
+  <si>
+    <t>DDL_target_002</t>
+  </si>
+  <si>
+    <t>创建目标成功（填写标题）</t>
+  </si>
+  <si>
+    <t>1.打开目标创建
+2.网络连接正常</t>
+  </si>
+  <si>
+    <t>1.点击“+”创建目标
+2.输入目标标题
+3.保存</t>
+  </si>
+  <si>
+    <t>标题：健身</t>
+  </si>
+  <si>
+    <t>目标创建成功</t>
+  </si>
+  <si>
+    <t>DDL_target_003</t>
+  </si>
+  <si>
+    <t>创建目标成功（不填写标题）</t>
+  </si>
+  <si>
+    <t>1.点击“+”创建目标
+2.不输入目标标题
+3.保存</t>
+  </si>
+  <si>
+    <t>提示，请输入目标标题</t>
+  </si>
+  <si>
+    <t>DDL_target_004</t>
+  </si>
+  <si>
+    <t>创建目标失败（开始时间晚于截止时间）</t>
+  </si>
+  <si>
+    <t>1.点击“+”创建目标
+2.输入目标标题
+3.设置时间
+4.保存</t>
+  </si>
+  <si>
+    <t>标题：健身
+开始时间2026.5.21
+结束时间：2026.5.50</t>
+  </si>
+  <si>
+    <t>目标创建失败，提示结束时间不能早于开始时间</t>
+  </si>
+  <si>
+    <t>DDL_target_005</t>
+  </si>
+  <si>
+    <t>AI目标规划助手创建目标</t>
+  </si>
+  <si>
+    <t>1.打开目标创建
+2.确认 AI 智能解析服务已正常连接
+3.网络连接正常</t>
+  </si>
+  <si>
+    <t>1.点击“+”创建目标
+2.与AI目标规划助手对话
+3.ai创建目标和对应任务
+4.保存</t>
+  </si>
+  <si>
+    <t>目标和对应任务创建成功</t>
+  </si>
+  <si>
+    <t>DDL_target_006</t>
+  </si>
+  <si>
+    <t>AI助手建议</t>
+  </si>
+  <si>
+    <t>1.打开目标栏
+2.网络连接正常</t>
+  </si>
+  <si>
+    <t>1.点击右下角AI</t>
+  </si>
+  <si>
+    <t>AI助手给出当前目标建议</t>
+  </si>
+  <si>
+    <t>DDL_target_007</t>
+  </si>
+  <si>
+    <t>删除目标</t>
+  </si>
+  <si>
+    <t>1.打开目标栏
+2.存在已创建的目标
+3.网络连接正常</t>
+  </si>
+  <si>
+    <t>左滑点击删除目标</t>
+  </si>
+  <si>
+    <t>目标被删除</t>
+  </si>
+  <si>
+    <t>DDL_target_008</t>
+  </si>
+  <si>
+    <t>目标进度变化</t>
+  </si>
+  <si>
+    <t>1.存在已创建的目标
+2.网络连接正常</t>
+  </si>
+  <si>
+    <t>1.完成目标的部分任务
+2.点击查看目标进度</t>
   </si>
   <si>
     <t>DDL_calendar_001</t>
@@ -766,6 +1270,36 @@
     <t>显示本月完成情况等内容</t>
   </si>
   <si>
+    <t xml:space="preserve"> DDL_statistics_003</t>
+  </si>
+  <si>
+    <t>AI效率诊断</t>
+  </si>
+  <si>
+    <t>1.存在任务
+2.网络连接正常</t>
+  </si>
+  <si>
+    <t>1.点击“统计”栏
+2.点击AI效率诊断</t>
+  </si>
+  <si>
+    <t>AI给出建议</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DDL_statistics_004</t>
+  </si>
+  <si>
+    <t>AI效率诊断（断网）</t>
+  </si>
+  <si>
+    <t>1.存在任务
+2.网络中断</t>
+  </si>
+  <si>
+    <t>网络无法连接</t>
+  </si>
+  <si>
     <t xml:space="preserve"> DDL_mine_001</t>
   </si>
   <si>
@@ -839,27 +1373,10 @@
     <t xml:space="preserve"> DDL_remind_001</t>
   </si>
   <si>
-    <t>开启微信订阅（点开开关）</t>
+    <t>开启邮箱提醒（点开开关）</t>
   </si>
   <si>
     <t>“我的”栏/提醒</t>
-  </si>
-  <si>
-    <t>1.网络连接正常
-2.已连通微信</t>
-  </si>
-  <si>
-    <t>1.点击“我的”菜单栏
-2.点击开启微信订阅开关</t>
-  </si>
-  <si>
-    <t>已打开微信订阅</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DDL_remind_002</t>
-  </si>
-  <si>
-    <t>开启邮箱提醒（点开开关）</t>
   </si>
   <si>
     <t>1.网络连接正常
@@ -873,7 +1390,7 @@
     <t>已打开邮箱提醒</t>
   </si>
   <si>
-    <t xml:space="preserve"> DDL_remind_004</t>
+    <t xml:space="preserve"> DDL_remind_002</t>
   </si>
   <si>
     <t>开启提前24h提醒（点开开关）</t>
@@ -886,7 +1403,7 @@
     <t>已打开提前24h提醒</t>
   </si>
   <si>
-    <t xml:space="preserve"> DDL_remind_005</t>
+    <t xml:space="preserve"> DDL_remind_003</t>
   </si>
   <si>
     <t>开启提前2h提醒（点开开关）</t>
@@ -940,7 +1457,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -977,6 +1494,12 @@
       <color rgb="FF0F1115"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1498,137 +2021,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1638,12 +2161,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1653,6 +2182,12 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1671,8 +2206,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2202,14 +2746,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K57"/>
+  <dimension ref="A1:K92"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="23.6363636363636" style="2" customWidth="1"/>
     <col min="2" max="2" width="44.9090909090909" style="2" customWidth="1"/>
     <col min="3" max="3" width="17.6363636363636" style="2" customWidth="1"/>
     <col min="4" max="4" width="10.0909090909091" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1818181818182" customWidth="1"/>
+    <col min="5" max="5" width="26.0909090909091" style="3" customWidth="1"/>
     <col min="6" max="6" width="31.9454545454545" customWidth="1"/>
     <col min="7" max="7" width="31.0090909090909" customWidth="1"/>
     <col min="8" max="8" width="39.8727272727273" customWidth="1"/>
@@ -2217,1466 +2761,2376 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.5" spans="1:11">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" ht="85" customHeight="1" spans="1:11">
+    <row r="3" ht="56" spans="1:11">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="9" t="s">
+      <c r="D3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" ht="39" customHeight="1" spans="1:11">
+    <row r="4" ht="56" spans="1:11">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="9" t="s">
+      <c r="D4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="H4" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" ht="56" spans="1:11">
+      <c r="A5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="B5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" ht="28" spans="1:11">
-      <c r="A5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="8" t="s">
+    <row r="6" ht="42" spans="1:11">
+      <c r="A6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="9" t="s">
+      <c r="D6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="9" t="s">
+      <c r="F6" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" ht="56" spans="1:11">
+      <c r="A7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" ht="56" spans="1:11">
-      <c r="A6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="8" t="s">
+      <c r="E7" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" ht="56" spans="1:11">
+      <c r="A8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="9" t="s">
+      <c r="D8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K6" t="s">
+      <c r="F8" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="42" spans="1:11">
-      <c r="A7" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="9" t="s">
+    <row r="9" ht="56" spans="1:11">
+      <c r="A9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" s="10" t="s">
+      <c r="F9" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="10" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="42" spans="1:11">
-      <c r="A8" s="11" t="s">
+      <c r="H9" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" ht="56" spans="1:11">
+      <c r="A10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B10" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="9" t="s">
+      <c r="C10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="9" t="s">
+      <c r="F10" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H10" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" ht="56" spans="1:11">
+      <c r="A11" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="42" spans="1:11">
-      <c r="A9" s="11" t="s">
+      <c r="B11" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="C11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="G9" s="9" t="s">
+      <c r="F11" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H11" s="10" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="42" spans="1:11">
-      <c r="A10" s="11" t="s">
+    <row r="12" ht="85" customHeight="1" spans="1:11">
+      <c r="A12" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B12" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10" s="9" t="s">
+      <c r="C12" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="D12" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="13" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="11" s="1" customFormat="1" ht="56" spans="1:11">
-      <c r="A11" s="8" t="s">
+      <c r="F12" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="G12" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="H12" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="9" t="s">
+    </row>
+    <row r="13" ht="39" customHeight="1" spans="1:11">
+      <c r="A13" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="B13" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="C13" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="13" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="28" spans="1:11">
-      <c r="A12" s="8" t="s">
+      <c r="G13" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="H13" s="14" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" ht="28" spans="1:11">
+      <c r="A14" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="9" t="s">
+      <c r="B14" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="C14" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" s="13" t="s">
         <v>60</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" customFormat="1" ht="42" spans="1:11">
-      <c r="A13" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="14" customFormat="1" ht="42" spans="1:11">
-      <c r="A14" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>72</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="H14" s="10" t="s">
+      <c r="H14" s="13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" ht="56" spans="1:11">
+      <c r="A15" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="H15" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="K15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="42" spans="1:11">
+      <c r="A16" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="G16" s="13" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="15" customFormat="1" ht="42" spans="1:11">
-      <c r="A15" s="2" t="s">
+      <c r="H16" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="B15" s="11" t="s">
+    </row>
+    <row r="17" s="1" customFormat="1" ht="42" spans="1:8">
+      <c r="A17" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F15" s="9" t="s">
+      <c r="B17" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="G15" s="13" t="s">
+      <c r="C17" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="G17" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="H15" s="10" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="16" customFormat="1" ht="42" spans="1:11">
-      <c r="A16" s="2" t="s">
+      <c r="H17" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="B16" s="11" t="s">
+    </row>
+    <row r="18" s="1" customFormat="1" ht="42" spans="1:8">
+      <c r="A18" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F16" s="9" t="s">
+      <c r="B18" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="G16" s="13"/>
-      <c r="H16" s="10" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="17" customFormat="1" ht="42" spans="1:8">
-      <c r="A17" s="2" t="s">
+      <c r="C18" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="G18" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="H18" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F17" s="9" t="s">
+    </row>
+    <row r="19" s="1" customFormat="1" ht="42" spans="1:8">
+      <c r="A19" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="G17" s="13"/>
-      <c r="H17" s="10" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="18" customFormat="1" ht="42" spans="1:8">
-      <c r="A18" s="2" t="s">
+      <c r="B19" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="C19" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="G19" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F18" s="9" t="s">
+      <c r="H19" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="G18" s="13"/>
-      <c r="H18" s="10" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="19" customFormat="1" ht="42" spans="1:8">
-      <c r="A19" s="2" t="s">
+    </row>
+    <row r="20" s="1" customFormat="1" ht="56" spans="1:8">
+      <c r="A20" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B20" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C20" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="D19" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F19" s="9" t="s">
+      <c r="D20" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="G19" s="13"/>
-      <c r="H19" s="10" t="s">
+      <c r="F20" s="13" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="20" ht="28" spans="1:8">
-      <c r="A20" s="2" t="s">
+      <c r="G20" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="H20" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="C20" s="8" t="s">
+    </row>
+    <row r="21" s="1" customFormat="1" ht="56" spans="1:8">
+      <c r="A21" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="D20" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F20" s="9" t="s">
+      <c r="B21" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="G20" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H20" s="10" t="s">
+      <c r="C21" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="G21" s="13" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="21" ht="28" spans="1:8">
-      <c r="A21" s="2" t="s">
+      <c r="H21" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="B21" s="8" t="s">
+    </row>
+    <row r="22" s="1" customFormat="1" ht="56" spans="1:8">
+      <c r="A22" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E21" s="9" t="s">
+      <c r="B22" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="C22" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="G22" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="G21" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H21" s="10" t="s">
+      <c r="H22" s="13" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="22" ht="28" spans="1:8">
-      <c r="A22" s="2" t="s">
+    <row r="23" s="1" customFormat="1" ht="56" spans="1:8">
+      <c r="A23" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B23" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22" s="9" t="s">
+      <c r="C23" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="G23" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="H23" s="13" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="56" spans="1:8">
+      <c r="A24" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="G22" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H22" s="10" t="s">
+      <c r="B24" s="16" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="23" ht="28" spans="1:8">
-      <c r="A23" s="2" t="s">
+      <c r="C24" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="G24" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="H24" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="C23" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E23" s="9" t="s">
+    </row>
+    <row r="25" s="1" customFormat="1" ht="56" spans="1:8">
+      <c r="A25" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="B25" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="G23" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H23" s="10" t="s">
+      <c r="C25" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="G25" s="13" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="2" t="s">
+      <c r="H25" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="B24" s="8" t="s">
+    </row>
+    <row r="26" s="1" customFormat="1" ht="56" spans="1:8">
+      <c r="A26" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="C24" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E24" s="10" t="s">
+      <c r="B26" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="F24" s="10" t="s">
+      <c r="C26" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="G26" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="G24" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H24" s="10" t="s">
+      <c r="H26" s="13" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="25" ht="28" spans="1:8">
-      <c r="A25" s="2" t="s">
+    <row r="27" s="1" customFormat="1" ht="56" spans="1:8">
+      <c r="A27" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B27" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="C25" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E25" s="9" t="s">
+      <c r="C27" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="G27" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="H27" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="G25" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H25" s="10" t="s">
+    </row>
+    <row r="28" s="1" customFormat="1" ht="56" spans="1:8">
+      <c r="A28" s="12" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="26" ht="42" spans="1:8">
-      <c r="A26" s="2" t="s">
+      <c r="B28" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="C28" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="G28" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="C26" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E26" s="9" t="s">
+      <c r="H28" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="F26" s="9" t="s">
+    </row>
+    <row r="29" s="1" customFormat="1" ht="56" spans="1:8">
+      <c r="A29" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="G26" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H26" s="9" t="s">
+      <c r="B29" s="16" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="27" ht="28" spans="1:8">
-      <c r="A27" s="2" t="s">
+      <c r="C29" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="G29" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="H29" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="C27" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E27" s="9" t="s">
+    </row>
+    <row r="30" s="1" customFormat="1" ht="56" spans="1:8">
+      <c r="A30" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="B30" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="G27" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H27" s="9" t="s">
+      <c r="C30" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="G30" s="13" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="28" ht="28" spans="1:8">
-      <c r="A28" s="2" t="s">
+      <c r="H30" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="B28" s="8" t="s">
+    </row>
+    <row r="31" s="1" customFormat="1" ht="56" spans="1:8">
+      <c r="A31" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="B31" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="D28" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E28" s="9" t="s">
+      <c r="C31" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="G31" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="F28" s="10" t="s">
+      <c r="H31" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="G28" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H28" s="10" t="s">
+    </row>
+    <row r="32" s="1" customFormat="1" ht="56" spans="1:8">
+      <c r="A32" s="12" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="29" ht="28" spans="1:8">
-      <c r="A29" s="2" t="s">
+      <c r="B32" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="C32" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="G32" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="C29" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E29" s="9" t="s">
+      <c r="H32" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="F29" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H29" s="10" t="s">
+    </row>
+    <row r="33" s="1" customFormat="1" ht="56" spans="1:8">
+      <c r="A33" s="12" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="30" ht="28" spans="1:8">
-      <c r="A30" s="2" t="s">
+      <c r="B33" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="C33" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="G33" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="H33" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="D30" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E30" s="9" t="s">
+    </row>
+    <row r="34" s="1" customFormat="1" ht="56" spans="1:8">
+      <c r="A34" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="F30" s="9" t="s">
+      <c r="B34" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="G30" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H30" s="10" t="s">
+      <c r="C34" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="G34" s="13" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="31" ht="42" spans="1:8">
-      <c r="A31" s="2" t="s">
+      <c r="H34" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B31" s="8" t="s">
+    </row>
+    <row r="35" s="1" customFormat="1" ht="56" spans="1:8">
+      <c r="A35" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="C31" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="F31" s="9" t="s">
+      <c r="B35" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="G31" s="10" t="s">
+      <c r="C35" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="F35" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="G35" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="H31" s="10" t="s">
+      <c r="H35" s="13" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="32" ht="42" spans="1:8">
-      <c r="A32" s="2" t="s">
+    <row r="36" s="1" customFormat="1" ht="56" spans="1:8">
+      <c r="A36" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B36" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="C32" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="G32" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="H32" s="10" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="33" ht="42" spans="1:8">
-      <c r="A33" s="2" t="s">
+      <c r="C36" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="F36" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="G36" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="H36" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="C33" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E33" s="9" t="s">
+    </row>
+    <row r="37" s="1" customFormat="1" ht="56" spans="1:8">
+      <c r="A37" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="F33" s="9" t="s">
+      <c r="B37" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="G33" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H33" s="10" t="s">
+      <c r="C37" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="F37" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="G37" s="13" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="34" ht="28" spans="1:8">
-      <c r="A34" s="2" t="s">
+      <c r="H37" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="B34" s="8" t="s">
+    </row>
+    <row r="38" s="1" customFormat="1" ht="56" spans="1:8">
+      <c r="A38" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="B38" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="D34" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E34" s="9" t="s">
+      <c r="C38" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="F34" s="10" t="s">
+      <c r="F38" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="G34" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H34" s="10" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="35" ht="28" spans="1:8">
-      <c r="A35" s="2" t="s">
+      <c r="G38" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="H38" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="B35" s="8" t="s">
+    </row>
+    <row r="39" s="1" customFormat="1" ht="28" spans="1:8">
+      <c r="A39" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="B39" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="D35" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="F35" s="10" t="s">
+      <c r="C39" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E39" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="G35" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H35" s="10" t="s">
+      <c r="F39" s="13" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="36" ht="28" spans="1:8">
-      <c r="A36" s="2" t="s">
+      <c r="G39" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="H39" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="C36" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E36" s="9" t="s">
+    </row>
+    <row r="40" customFormat="1" ht="42" spans="1:8">
+      <c r="A40" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="F36" s="9" t="s">
+      <c r="B40" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="G36" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H36" s="10" t="s">
+      <c r="C40" s="12" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="37" ht="28" spans="1:8">
-      <c r="A37" s="2" t="s">
+      <c r="D40" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E40" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="F40" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="C37" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="F37" s="9" t="s">
+      <c r="G40" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="G37" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H37" s="10" t="s">
+      <c r="H40" s="14" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="38" ht="28" spans="1:8">
-      <c r="A38" s="2" t="s">
+    <row r="41" customFormat="1" ht="42" spans="1:8">
+      <c r="A41" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B41" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C41" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E41" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="F41" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="D38" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="F38" s="9" t="s">
+      <c r="G41" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="H41" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="G38" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H38" s="10" t="s">
+    </row>
+    <row r="42" customFormat="1" ht="42" spans="1:8">
+      <c r="A42" s="2" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="39" ht="28" spans="1:8">
-      <c r="A39" s="2" t="s">
+      <c r="B42" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="C42" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E42" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="F42" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="G42" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="D39" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="F39" s="9" t="s">
+      <c r="H42" s="14" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="43" customFormat="1" ht="42" spans="1:8">
+      <c r="A43" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="G39" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H39" s="10" t="s">
+      <c r="B43" s="15" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="40" ht="42" spans="1:8">
-      <c r="A40" s="2" t="s">
+      <c r="C43" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="F43" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="B40" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E40" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="F40" s="9" t="s">
+      <c r="G43" s="17"/>
+      <c r="H43" s="14" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="44" customFormat="1" ht="42" spans="1:8">
+      <c r="A44" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="G40" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H40" s="10" t="s">
+      <c r="B44" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="C44" s="12" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="41" ht="42" spans="1:8">
-      <c r="A41" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="B41" s="8" t="s">
+      <c r="D44" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="F44" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="C41" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E41" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="F41" s="9" t="s">
+      <c r="G44" s="17"/>
+      <c r="H44" s="14" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="45" customFormat="1" ht="42" spans="1:8">
+      <c r="A45" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="G41" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H41" s="10" t="s">
+      <c r="B45" s="15" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="42" ht="28" spans="1:8">
-      <c r="A42" s="2" t="s">
+      <c r="C45" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E45" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="F45" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="G45" s="17"/>
+      <c r="H45" s="14" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="46" customFormat="1" ht="42" spans="1:8">
+      <c r="A46" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="B46" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="D42" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E42" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="F42" s="9" t="s">
+      <c r="C46" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="G42" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H42" s="10" t="s">
+      <c r="D46" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E46" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="F46" s="13" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="43" ht="42" spans="1:8">
-      <c r="A43" s="2" t="s">
+      <c r="G46" s="17"/>
+      <c r="H46" s="14" t="s">
         <v>200</v>
       </c>
-      <c r="B43" s="8" t="s">
+    </row>
+    <row r="47" ht="28" spans="1:8">
+      <c r="A47" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C43" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E43" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="F43" s="9" t="s">
+      <c r="B47" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="G43" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H43" s="10" t="s">
+      <c r="C47" s="12" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="44" ht="42" spans="1:8">
-      <c r="A44" s="2" t="s">
+      <c r="D47" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E47" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="F47" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="G47" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="H47" s="14" t="s">
         <v>205</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E44" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="F44" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="G44" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H44" s="10" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="45" ht="28" spans="1:8">
-      <c r="A45" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="F45" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="G45" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="46" ht="28" spans="1:8">
-      <c r="A46" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E46" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="F46" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="G46" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H46" s="10" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
-      <c r="A47" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E47" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="F47" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="G47" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="H47" s="14" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="48" ht="28" spans="1:8">
       <c r="A48" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="D48" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E48" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="F48" s="15" t="s">
-        <v>227</v>
+        <v>206</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E48" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="F48" s="13" t="s">
+        <v>209</v>
       </c>
       <c r="G48" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="H48" t="s">
-        <v>228</v>
+        <v>170</v>
+      </c>
+      <c r="H48" s="14" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="49" ht="28" spans="1:8">
       <c r="A49" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E49" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="F49" s="15" t="s">
-        <v>231</v>
+        <v>211</v>
+      </c>
+      <c r="B49" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E49" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="F49" s="13" t="s">
+        <v>214</v>
       </c>
       <c r="G49" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="H49" t="s">
-        <v>232</v>
+        <v>170</v>
+      </c>
+      <c r="H49" s="14" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="50" ht="28" spans="1:8">
       <c r="A50" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="C50" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="B50" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E50" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="F50" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="G50" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="H50" s="14" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="D50" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E50" s="14" t="s">
+      <c r="B51" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="F50" s="15" t="s">
-        <v>235</v>
-      </c>
-      <c r="G50" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="H50" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="51" ht="28" spans="1:8">
-      <c r="A51" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="D51" s="8" t="s">
+      <c r="C51" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="D51" s="12" t="s">
         <v>12</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="F51" s="15" t="s">
-        <v>239</v>
+        <v>223</v>
+      </c>
+      <c r="F51" s="14" t="s">
+        <v>224</v>
       </c>
       <c r="G51" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="H51" t="s">
-        <v>240</v>
+        <v>170</v>
+      </c>
+      <c r="H51" s="14" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="52" ht="28" spans="1:8">
       <c r="A52" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="D52" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E52" s="15" t="s">
-        <v>244</v>
-      </c>
-      <c r="F52" s="15" t="s">
-        <v>245</v>
+        <v>226</v>
+      </c>
+      <c r="B52" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E52" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="F52" s="13" t="s">
+        <v>229</v>
       </c>
       <c r="G52" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="H52" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="53" ht="28" spans="1:8">
+        <v>170</v>
+      </c>
+      <c r="H52" s="14" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="53" ht="42" spans="1:8">
       <c r="A53" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="D53" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E53" s="15" t="s">
-        <v>249</v>
-      </c>
-      <c r="F53" s="15" t="s">
-        <v>250</v>
+        <v>231</v>
+      </c>
+      <c r="B53" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E53" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="F53" s="13" t="s">
+        <v>234</v>
       </c>
       <c r="G53" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="H53" t="s">
-        <v>251</v>
+        <v>170</v>
+      </c>
+      <c r="H53" s="13" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="54" ht="28" spans="1:8">
       <c r="A54" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="D54" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E54" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="F54" s="15" t="s">
-        <v>254</v>
+        <v>236</v>
+      </c>
+      <c r="B54" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E54" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="F54" s="13" t="s">
+        <v>239</v>
       </c>
       <c r="G54" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="H54" t="s">
-        <v>255</v>
+        <v>170</v>
+      </c>
+      <c r="H54" s="13" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="55" ht="28" spans="1:8">
       <c r="A55" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B55" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E55" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="F55" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="G55" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="H55" s="14" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="56" ht="28" spans="1:8">
+      <c r="A56" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B56" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E56" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="F56" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="G56" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="H56" s="14" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="57" ht="28" spans="1:8">
+      <c r="A57" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B57" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E57" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="F57" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="G57" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="H57" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="B55" s="2" t="s">
+    </row>
+    <row r="58" ht="42" spans="1:8">
+      <c r="A58" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="C55" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="D55" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E55" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="F55" s="15" t="s">
+      <c r="B58" s="12" t="s">
         <v>258</v>
       </c>
-      <c r="G55" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="H55" t="s">
+      <c r="C58" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E58" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="F58" s="13" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="56" ht="42" spans="1:8">
-      <c r="A56" s="2" t="s">
+      <c r="G58" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="H58" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="C56" s="8" t="s">
+    </row>
+    <row r="59" ht="42" spans="1:8">
+      <c r="A59" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="D56" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E56" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="F56" s="15" t="s">
+      <c r="B59" s="12" t="s">
         <v>263</v>
       </c>
-      <c r="G56" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="H56" t="s">
+      <c r="C59" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E59" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="F59" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="G59" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="H59" s="14" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="60" ht="42" spans="1:8">
+      <c r="A60" s="2" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="57" ht="42" spans="1:8">
-      <c r="A57" s="2" t="s">
+      <c r="B60" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="C60" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E60" s="13" t="s">
         <v>266</v>
       </c>
-      <c r="C57" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="D57" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E57" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="F57" s="15" t="s">
+      <c r="F60" s="13" t="s">
         <v>267</v>
       </c>
-      <c r="G57" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="H57" t="s">
+      <c r="G60" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="H60" s="14" t="s">
         <v>268</v>
+      </c>
+    </row>
+    <row r="61" ht="28" spans="1:8">
+      <c r="A61" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="B61" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E61" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="F61" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="G61" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="H61" s="14" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="62" ht="42" spans="1:8">
+      <c r="A62" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="B62" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E62" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="F62" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="G62" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="H62" s="14" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="63" ht="42" spans="1:8">
+      <c r="A63" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="B63" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="C63" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E63" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="F63" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="G63" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="H63" s="14" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="64" ht="56" spans="1:8">
+      <c r="A64" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="B64" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="D64" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E64" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="F64" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="G64" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="H64" s="13" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="65" ht="56" spans="1:8">
+      <c r="A65" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="B65" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E65" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="F65" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="G65" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="H65" s="14" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="66" ht="28" spans="1:8">
+      <c r="A66" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="B66" s="15" t="s">
+        <v>295</v>
+      </c>
+      <c r="C66" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E66" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="F66" s="13" t="s">
+        <v>297</v>
+      </c>
+      <c r="G66" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="H66" s="14" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="67" ht="42" spans="1:8">
+      <c r="A67" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="B67" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E67" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="F67" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="G67" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="H67" s="14" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="68" ht="28" spans="1:8">
+      <c r="A68" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="B68" s="18" t="s">
+        <v>305</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E68" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="F68" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="G68" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="H68" s="14" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="69" ht="28" spans="1:8">
+      <c r="A69" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B69" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E69" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="F69" s="14" t="s">
+        <v>311</v>
+      </c>
+      <c r="G69" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="H69" s="14" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="70" ht="28" spans="1:8">
+      <c r="A70" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B70" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E70" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="F70" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="G70" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="H70" s="14" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="71" ht="28" spans="1:8">
+      <c r="A71" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B71" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E71" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="F71" s="13" t="s">
+        <v>320</v>
+      </c>
+      <c r="G71" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="H71" s="14" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="72" ht="28" spans="1:8">
+      <c r="A72" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B72" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="C72" s="12" t="s">
+        <v>324</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E72" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="F72" s="13" t="s">
+        <v>325</v>
+      </c>
+      <c r="G72" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="H72" s="14" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="73" ht="28" spans="1:8">
+      <c r="A73" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="B73" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E73" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="F73" s="13" t="s">
+        <v>330</v>
+      </c>
+      <c r="G73" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="H73" s="14" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="74" ht="42" spans="1:8">
+      <c r="A74" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B74" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="C74" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="D74" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E74" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="F74" s="13" t="s">
+        <v>333</v>
+      </c>
+      <c r="G74" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="H74" s="14" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="75" ht="42" spans="1:8">
+      <c r="A75" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B75" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E75" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="F75" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="G75" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="H75" s="14" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="76" ht="28" spans="1:8">
+      <c r="A76" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B76" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="C76" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="D76" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E76" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="F76" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="G76" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="H76" s="14" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="77" ht="42" spans="1:8">
+      <c r="A77" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B77" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="D77" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E77" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="F77" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="G77" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="H77" s="14" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="78" ht="42" spans="1:8">
+      <c r="A78" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B78" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="C78" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="D78" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E78" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="F78" s="13" t="s">
+        <v>349</v>
+      </c>
+      <c r="G78" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="H78" s="14" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="79" ht="28" spans="1:8">
+      <c r="A79" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B79" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="D79" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E79" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="F79" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="G79" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="H79" s="14" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="80" ht="28" spans="1:8">
+      <c r="A80" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B80" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="C80" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="D80" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E80" s="13" t="s">
+        <v>359</v>
+      </c>
+      <c r="F80" s="13" t="s">
+        <v>360</v>
+      </c>
+      <c r="G80" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="H80" s="14" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="81" ht="28" spans="1:8">
+      <c r="A81" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B81" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="C81" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="D81" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E81" s="19" t="s">
+        <v>364</v>
+      </c>
+      <c r="F81" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="G81" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="H81" s="20" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="82" ht="28" spans="1:8">
+      <c r="A82" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B82" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="C82" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="D82" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E82" s="19" t="s">
+        <v>369</v>
+      </c>
+      <c r="F82" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="G82" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="H82" s="20" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B83" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="C83" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="D83" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E83" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="F83" s="20" t="s">
+        <v>375</v>
+      </c>
+      <c r="G83" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="H83" s="20" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="84" ht="28" spans="1:8">
+      <c r="A84" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="C84" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="D84" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E84" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="F84" s="22" t="s">
+        <v>379</v>
+      </c>
+      <c r="G84" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="H84" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="85" ht="28" spans="1:8">
+      <c r="A85" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="D85" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E85" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="F85" s="22" t="s">
+        <v>383</v>
+      </c>
+      <c r="G85" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="H85" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="86" ht="28" spans="1:8">
+      <c r="A86" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="C86" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="D86" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E86" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="F86" s="22" t="s">
+        <v>387</v>
+      </c>
+      <c r="G86" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="H86" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="87" ht="28" spans="1:8">
+      <c r="A87" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="C87" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="D87" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E87" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="F87" s="22" t="s">
+        <v>391</v>
+      </c>
+      <c r="G87" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="H87" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="88" ht="28" spans="1:8">
+      <c r="A88" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="C88" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="D88" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E88" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="F88" s="22" t="s">
+        <v>397</v>
+      </c>
+      <c r="G88" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="H88" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="89" ht="28" spans="1:8">
+      <c r="A89" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="C89" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="D89" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E89" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="F89" s="22" t="s">
+        <v>401</v>
+      </c>
+      <c r="G89" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="H89" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="90" ht="28" spans="1:8">
+      <c r="A90" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="C90" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="D90" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E90" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="F90" s="22" t="s">
+        <v>405</v>
+      </c>
+      <c r="G90" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="H90" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="91" ht="42" spans="1:8">
+      <c r="A91" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="C91" s="12" t="s">
+        <v>409</v>
+      </c>
+      <c r="D91" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E91" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="F91" s="22" t="s">
+        <v>410</v>
+      </c>
+      <c r="G91" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="H91" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="92" ht="42" spans="1:8">
+      <c r="A92" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C92" s="12" t="s">
+        <v>409</v>
+      </c>
+      <c r="D92" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E92" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="F92" s="22" t="s">
+        <v>414</v>
+      </c>
+      <c r="G92" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="H92" t="s">
+        <v>415</v>
       </c>
     </row>
   </sheetData>
